--- a/benchmarks/RANDOM_FOREST_V3_FORECASTING/rf_results.xlsx
+++ b/benchmarks/RANDOM_FOREST_V3_FORECASTING/rf_results.xlsx
@@ -473,13 +473,13 @@
         <v>2021</v>
       </c>
       <c r="D2" t="n">
-        <v>6.552794206925666</v>
+        <v>6.562782371080473</v>
       </c>
       <c r="E2" t="n">
-        <v>29.23205311250231</v>
+        <v>29.4456579353806</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6299674727341145</v>
+        <v>0.6303519277910598</v>
       </c>
     </row>
     <row r="3">
@@ -493,13 +493,13 @@
         <v>2022</v>
       </c>
       <c r="D3" t="n">
-        <v>16.36565850738203</v>
+        <v>16.87686660875587</v>
       </c>
       <c r="E3" t="n">
-        <v>75.70336880210179</v>
+        <v>76.86852699857585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5913880429628708</v>
+        <v>0.5902201273355905</v>
       </c>
     </row>
     <row r="4">
@@ -513,13 +513,13 @@
         <v>2023</v>
       </c>
       <c r="D4" t="n">
-        <v>17.79772171200426</v>
+        <v>16.67672178850516</v>
       </c>
       <c r="E4" t="n">
-        <v>76.26475534029605</v>
+        <v>71.80644372249336</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6119310725271992</v>
+        <v>0.641068872399807</v>
       </c>
     </row>
     <row r="5">
@@ -533,13 +533,13 @@
         <v>2024</v>
       </c>
       <c r="D5" t="n">
-        <v>46.18498359030526</v>
+        <v>45.13110719824886</v>
       </c>
       <c r="E5" t="n">
-        <v>163.7391646183551</v>
+        <v>165.4515612889732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6106658855344113</v>
+        <v>0.6138947754087261</v>
       </c>
     </row>
     <row r="6">
@@ -553,13 +553,13 @@
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>18.24864189980959</v>
+        <v>16.75156073139258</v>
       </c>
       <c r="E6" t="n">
-        <v>54.07784086022642</v>
+        <v>52.49765924228642</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7794268270261904</v>
+        <v>0.7921290107019411</v>
       </c>
     </row>
   </sheetData>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.02995998328536</v>
+        <v>20.39980773959659</v>
       </c>
       <c r="C2" t="n">
-        <v>14.85178730294646</v>
+        <v>14.51449821218379</v>
       </c>
     </row>
     <row r="3">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.80343654669635</v>
+        <v>79.21396983754188</v>
       </c>
       <c r="C3" t="n">
-        <v>50.72920845770767</v>
+        <v>51.69124888705274</v>
       </c>
     </row>
     <row r="4">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6446758601569572</v>
+        <v>0.6535329427274249</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0765549650330208</v>
+        <v>0.07981428359296688</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1667468289056692</v>
+        <v>0.1614006486542045</v>
       </c>
     </row>
     <row r="3">
@@ -675,17 +675,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1196442460482502</v>
+        <v>0.1139218538597339</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>casos_roll4_mean</t>
+          <t>casos_lag_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1170564531513578</v>
+        <v>0.1054716291791916</v>
       </c>
     </row>
     <row r="5">
@@ -695,17 +695,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09786634056900975</v>
+        <v>0.1026406052969285</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>casos_lag_2</t>
+          <t>casos_roll4_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08916606408535289</v>
+        <v>0.08740282847316991</v>
       </c>
     </row>
     <row r="7">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05540622116433253</v>
+        <v>0.07522892247074069</v>
       </c>
     </row>
     <row r="8">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03812042603974127</v>
+        <v>0.04661860741059039</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03777722031109394</v>
+        <v>0.03410324143428042</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02817060751429935</v>
+        <v>0.02795700526585043</v>
       </c>
     </row>
     <row r="11">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02096420384946992</v>
+        <v>0.02247691456956153</v>
       </c>
     </row>
     <row r="12">
@@ -765,147 +765,147 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02017990874867563</v>
+        <v>0.0206420740217637</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>semana</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01839065539865665</v>
+        <v>0.01998324787427709</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>area_km2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01234030055557649</v>
+        <v>0.0152753698760541</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pct_builtup</t>
+          <t>casos_lag_8</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01222072872435425</v>
+        <v>0.01484040363524325</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>area_km2</t>
+          <t>pct_builtup</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01202103389523282</v>
+        <v>0.01474652168714581</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>median_age</t>
+          <t>n_pixels</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01149821586136073</v>
+        <v>0.01182051415007592</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>n_pixels</t>
+          <t>median_age</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01123743322251356</v>
+        <v>0.009982202062906518</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>casos_lag_8</t>
+          <t>aging_index</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.01052641464807056</v>
+        <v>0.007797638134507434</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>anio</t>
+          <t>female_population_pct</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.009416452321737254</v>
+        <v>0.007364625705895775</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aging_index</t>
+          <t>sex_ratio</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.008927946653097141</v>
+        <v>0.007328027003413587</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>female_population_pct</t>
+          <t>male_population_pct</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.00771541517717621</v>
+        <v>0.006941344450405363</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sex_ratio</t>
+          <t>nino34</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.006856795390973505</v>
+        <v>0.006918963580659923</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>male_population_pct</t>
+          <t>pct_cropland</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.006772792046941716</v>
+        <v>0.006405473021759023</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nino34</t>
+          <t>EVI_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005482822084865895</v>
+        <v>0.005107834379046926</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pct_cropland</t>
+          <t>pct_wetland</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.005446836649184239</v>
+        <v>0.004526879690554021</v>
       </c>
     </row>
     <row r="27">
@@ -915,17 +915,17 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.005144913605041797</v>
+        <v>0.004465724890306304</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pct_wetland</t>
+          <t>precip_roll8_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.004587989295467661</v>
+        <v>0.003830622398165812</v>
       </c>
     </row>
     <row r="29">
@@ -935,207 +935,207 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.00422498984754982</v>
+        <v>0.003525480721328246</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EVI_mean</t>
+          <t>LST_Night_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.003816200868541059</v>
+        <v>0.002784931650206337</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>precip_roll8_sum</t>
+          <t>soi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.003082618543426165</v>
+        <v>0.002717514459261588</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LST_Night_mean</t>
+          <t>pct_shrubland</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002753691406909006</v>
+        <v>0.002569617313460989</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NDVI_std</t>
+          <t>LST_Day_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002542101871109758</v>
+        <v>0.002445815364456759</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>elev_min</t>
+          <t>precip_roll4_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.002535747869025001</v>
+        <v>0.002364933803163267</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>elev_max</t>
+          <t>tempmed_roll8_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002499211022722245</v>
+        <v>0.002364274699486207</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pct_tree_cover</t>
+          <t>elev_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.002219736528048849</v>
+        <v>0.002198144694244142</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LST_Day_mean</t>
+          <t>tempmed_roll4_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.002062077254461318</v>
+        <v>0.002197059458211681</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NDVI_mean</t>
+          <t>pct_tree_cover</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.002048819748069542</v>
+        <v>0.002164892466982194</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>garbage_collection_pct</t>
+          <t>NDVI_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.002025898385303866</v>
+        <v>0.002071146529199759</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pct_shrubland</t>
+          <t>NDVI_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.002009424725267344</v>
+        <v>0.002024856409411484</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>precip_roll4_sum</t>
+          <t>garbage_collection_pct</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.001960404723397961</v>
+        <v>0.001886187349382123</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>water_supply_pct</t>
+          <t>elev_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.001850215481304689</v>
+        <v>0.001799706494809232</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>soi</t>
+          <t>water_supply_pct</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.001801772082965888</v>
+        <v>0.001688165153265485</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tempmed_roll8_mean</t>
+          <t>sewage_pct</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.001652988657428622</v>
+        <v>0.001679989883597612</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sewage_pct</t>
+          <t>LST_Day_std</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.001528118237465157</v>
+        <v>0.001539506626935121</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tempmed_roll4_mean</t>
+          <t>tempmin</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.00138376633472481</v>
+        <v>0.001392657233560153</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pct_water</t>
+          <t>n_tiles</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.001353773265818361</v>
+        <v>0.001174967415725804</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tempmin</t>
+          <t>precip_total_semana_lag_4</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.001248127125291411</v>
+        <v>0.001146191020202529</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LST_Day_std</t>
+          <t>tempmed_lag_1</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.00118991871634412</v>
+        <v>0.001134173209826834</v>
       </c>
     </row>
     <row r="50">
@@ -1145,117 +1145,117 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.001023411288100926</v>
+        <v>0.001050026624844617</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tempmed_lag_1</t>
+          <t>EVI_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0009997264953239338</v>
+        <v>0.001026223551462893</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tempmed</t>
+          <t>pct_water</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0009736154910956069</v>
+        <v>0.0009464576132258453</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>pct_grassland</t>
+          <t>tempmed</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0009713430934090106</v>
+        <v>0.0009275977405016764</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tempmed_lag_4</t>
+          <t>pct_grassland</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0009610331814840329</v>
+        <v>0.000921017071239812</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>precip_total_semana_lag_4</t>
+          <t>precip_total_semana_lag_1</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0008934768565852571</v>
+        <v>0.0008561724656950961</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EVI_std</t>
+          <t>tempmed_lag_4</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.000883552320185225</v>
+        <v>0.0007738207626776298</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>n_tiles</t>
+          <t>tempmax</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0008834081372535985</v>
+        <v>0.0007596039967870856</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>precip_total_semana_lag_1</t>
+          <t>precip_total_semana</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.000795006756733424</v>
+        <v>0.0006510364197129061</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tempmax</t>
+          <t>umidmin</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0007441632991771589</v>
+        <v>0.0006130596271787289</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>precip_max_semana</t>
+          <t>umidmed_lag_4</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0006730452301990002</v>
+        <v>0.0005597576250455153</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>precip_total_semana</t>
+          <t>precip_max_semana</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0006655915859996007</v>
+        <v>0.0005259165849189863</v>
       </c>
     </row>
     <row r="62">
@@ -1265,77 +1265,57 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0006599890174236051</v>
+        <v>0.0005082773904287591</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>precip_media_semana</t>
+          <t>umidmed</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0006463070730578527</v>
+        <v>0.0004906638693464614</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>umidmed_lag_4</t>
+          <t>precip_media_semana</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0006419396379189448</v>
+        <v>0.0004771079426500641</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>umidmin</t>
+          <t>umidmed_lag_1</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0005666301497391967</v>
+        <v>0.000477039735881532</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>umidmed_lag_1</t>
+          <t>pct_mangroves</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0005593971696890521</v>
+        <v>0.0001864036073442698</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>umidmed</t>
+          <t>dias_lluvia_semana</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0005157952430103276</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>dias_lluvia_semana</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.0002456580620972392</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>pct_mangroves</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0.0002220412988389561</v>
+        <v>0.0001798822379081867</v>
       </c>
     </row>
   </sheetData>
